--- a/2026_Kim-Min-seok/mail/130firiem.xlsx
+++ b/2026_Kim-Min-seok/mail/130firiem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Projects\Robocup_2026_Kim-Min-seok\mail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E84E769-7310-41BE-9F88-9F271C59AAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E939F297-CF7F-430C-9AFC-738A331C702C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{B379896D-38C1-45A3-88D3-7BAB00D45A12}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{B379896D-38C1-45A3-88D3-7BAB00D45A12}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="135">
   <si>
     <t>hello@365.bank</t>
   </si>
@@ -350,9 +350,6 @@
     <t>sales@csm.sk</t>
   </si>
   <si>
-    <t>info@csob.sk</t>
-  </si>
-  <si>
     <t>topec@topec.sk</t>
   </si>
   <si>
@@ -438,6 +435,15 @@
   </si>
   <si>
     <t>C:\Dev\Projects\Robocup_2026_Kim-Min-seok\mail\Tim_XLC_poster.pdf</t>
+  </si>
+  <si>
+    <t>jbohunicky1@gmail.com</t>
+  </si>
+  <si>
+    <t>martinsuriak2005@gmail.com</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -590,7 +596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -697,452 +703,13 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1513,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2DEA27-F914-4913-BE71-D11CD1F649D8}">
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.26953125" bestFit="1" customWidth="1"/>
@@ -1523,10 +1090,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
@@ -1537,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4"/>
@@ -1548,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1559,7 +1126,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="4"/>
@@ -1570,7 +1137,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
@@ -1581,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1592,7 +1159,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1603,7 +1170,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
@@ -1614,7 +1181,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="8"/>
@@ -1625,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -1636,7 +1203,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1647,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1658,7 +1225,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -1669,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -1680,7 +1247,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1691,7 +1258,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1702,7 +1269,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="12"/>
@@ -1713,7 +1280,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1724,7 +1291,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
@@ -1735,7 +1302,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -1746,7 +1313,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
@@ -1757,7 +1324,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="19"/>
@@ -1768,7 +1335,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="20"/>
@@ -1779,7 +1346,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="2"/>
@@ -1790,7 +1357,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -1801,7 +1368,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="19"/>
@@ -1812,7 +1379,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="12"/>
@@ -1823,7 +1390,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="10"/>
@@ -1834,7 +1401,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="15"/>
@@ -1845,7 +1412,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -1856,7 +1423,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -1867,7 +1434,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1878,7 +1445,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="8"/>
@@ -1889,7 +1456,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -1900,7 +1467,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="8"/>
@@ -1911,7 +1478,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -1922,7 +1489,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -1933,7 +1500,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="10"/>
@@ -1944,7 +1511,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="15"/>
@@ -1955,7 +1522,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="15"/>
@@ -1966,7 +1533,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -1977,7 +1544,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -1988,7 +1555,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="8"/>
@@ -1999,7 +1566,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -2010,7 +1577,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -2021,7 +1588,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="15"/>
@@ -2032,7 +1599,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
@@ -2043,7 +1610,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -2054,7 +1621,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C49" s="18"/>
       <c r="D49" s="19"/>
@@ -2065,7 +1632,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="15"/>
@@ -2076,7 +1643,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="8"/>
@@ -2087,7 +1654,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="20"/>
@@ -2098,7 +1665,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -2109,7 +1676,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -2120,7 +1687,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="19"/>
@@ -2131,7 +1698,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -2142,7 +1709,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -2153,7 +1720,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -2164,7 +1731,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="8"/>
@@ -2175,7 +1742,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="2"/>
@@ -2186,7 +1753,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="8"/>
@@ -2197,7 +1764,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -2208,7 +1775,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="17"/>
       <c r="D63" s="25"/>
@@ -2219,7 +1786,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -2230,7 +1797,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -2241,7 +1808,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -2252,7 +1819,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C67" s="21"/>
       <c r="D67" s="26"/>
@@ -2263,7 +1830,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -2274,7 +1841,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -2285,7 +1852,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -2296,7 +1863,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -2307,7 +1874,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -2318,7 +1885,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -2329,7 +1896,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C74" s="21"/>
       <c r="D74" s="26"/>
@@ -2340,7 +1907,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -2351,7 +1918,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
@@ -2362,7 +1929,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="8"/>
@@ -2373,7 +1940,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C78" s="18"/>
       <c r="D78" s="19"/>
@@ -2384,7 +1951,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -2395,7 +1962,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C80" s="17"/>
       <c r="D80" s="25"/>
@@ -2406,7 +1973,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -2417,7 +1984,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
@@ -2428,7 +1995,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -2439,7 +2006,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
@@ -2450,7 +2017,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C85" s="21"/>
       <c r="D85" s="26"/>
@@ -2461,7 +2028,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
@@ -2472,7 +2039,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="10"/>
@@ -2483,7 +2050,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="12"/>
@@ -2494,7 +2061,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="20"/>
@@ -2505,7 +2072,7 @@
         <v>88</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C90" s="28"/>
       <c r="D90" s="29"/>
@@ -2516,7 +2083,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -2527,7 +2094,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="8"/>
@@ -2538,7 +2105,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="8"/>
@@ -2549,7 +2116,7 @@
         <v>92</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
@@ -2560,7 +2127,7 @@
         <v>93</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C95" s="18"/>
       <c r="D95" s="19"/>
@@ -2571,7 +2138,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
@@ -2582,7 +2149,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="8"/>
@@ -2593,7 +2160,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -2604,7 +2171,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -2615,7 +2182,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C100" s="28"/>
       <c r="D100" s="29"/>
@@ -2626,7 +2193,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="10"/>
@@ -2637,7 +2204,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
@@ -2648,7 +2215,7 @@
         <v>101</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -2659,7 +2226,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="2"/>
@@ -2667,10 +2234,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="30" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C105" s="31"/>
       <c r="D105" s="31"/>
@@ -2678,10 +2245,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C106" s="22"/>
       <c r="D106" s="32"/>
@@ -2689,10 +2256,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="20"/>
@@ -2700,10 +2267,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C108" s="22"/>
       <c r="D108" s="32"/>
@@ -2711,10 +2278,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -2722,10 +2289,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C110" s="18"/>
       <c r="D110" s="19"/>
@@ -2733,10 +2300,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
@@ -2744,10 +2311,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="8"/>
@@ -2755,10 +2322,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -2766,10 +2333,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -2777,10 +2344,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -2788,10 +2355,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -2799,10 +2366,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C117" s="33"/>
       <c r="D117" s="34"/>
@@ -2810,10 +2377,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C118" s="21"/>
       <c r="D118" s="26"/>
@@ -2821,10 +2388,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C119" s="14"/>
       <c r="D119" s="15"/>
@@ -2832,10 +2399,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
@@ -2843,10 +2410,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C121" s="11"/>
       <c r="D121" s="12"/>
@@ -2854,10 +2421,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C122" s="18"/>
       <c r="D122" s="19"/>
@@ -2865,10 +2432,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
@@ -2876,10 +2443,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
@@ -2887,10 +2454,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C125" s="35"/>
       <c r="D125" s="35"/>
@@ -2898,10 +2465,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C126" s="35"/>
       <c r="D126" s="35"/>
@@ -2909,10 +2476,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" s="35"/>
       <c r="D127" s="35"/>
@@ -2920,10 +2487,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C128" s="22"/>
       <c r="D128" s="32"/>
@@ -2931,10 +2498,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C129" s="36"/>
       <c r="D129" s="37"/>
@@ -2942,32 +2509,48 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" s="16" t="s">
         <v>132</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A48">
-    <cfRule type="duplicateValues" dxfId="47" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A74">
-    <cfRule type="duplicateValues" dxfId="46" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A94">
-    <cfRule type="duplicateValues" dxfId="45" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B131">
-    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
+  <conditionalFormatting sqref="B1:B133">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A18" r:id="rId1" xr:uid="{B351FE46-7A30-4B23-A991-06B3862351E1}"/>
@@ -3012,6 +2595,8 @@
     <hyperlink ref="A129" r:id="rId40" xr:uid="{42696803-94D5-478B-807C-0B157F1F892A}"/>
     <hyperlink ref="A127" r:id="rId41" display="mailto:info@mhth.sk" xr:uid="{8BAED12F-21F5-4866-886F-87EB555B324B}"/>
     <hyperlink ref="A130" r:id="rId42" display="mailto:ondrej.marko@duslo.sk" xr:uid="{F7582A4B-C9D4-4527-B01C-3A75D2B70F65}"/>
+    <hyperlink ref="A132" r:id="rId43" xr:uid="{F2A15183-9A88-4DD2-9680-64487AE0759B}"/>
+    <hyperlink ref="A133" r:id="rId44" xr:uid="{F8588EC1-E8A1-4E23-9F45-B72AC1DAE604}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
